--- a/110-creation-exemples/ig/StructureDefinition-as-ext-smartcard.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-smartcard.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:21:44+00:00</t>
+    <t>2024-07-01T16:22:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-smartcard.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-smartcard.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T16:22:22+00:00</t>
+    <t>2024-07-02T08:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -323,6 +323,9 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Extension.extension:type</t>
   </si>
   <si>
@@ -369,9 +372,6 @@
     <t>Extension.url</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Extension.extension:type.value[x]</t>
   </si>
   <si>
@@ -487,8 +487,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t xml:space="preserve">per-1
-</t>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t>./low</t>
@@ -1324,24 +1324,24 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>76</v>
@@ -1366,10 +1366,10 @@
         <v>92</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1429,7 +1429,7 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>82</v>
@@ -1440,10 +1440,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1543,10 +1543,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1575,7 +1575,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1635,7 +1635,7 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>82</v>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1672,16 +1672,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>76</v>
@@ -1731,7 +1731,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>84</v>
@@ -1746,7 +1746,7 @@
         <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -1841,13 +1841,13 @@
         <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>124</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -1886,7 +1886,7 @@
         <v>127</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1946,7 +1946,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>82</v>
@@ -1960,7 +1960,7 @@
         <v>128</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2063,7 +2063,7 @@
         <v>129</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2092,7 +2092,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2152,7 +2152,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>82</v>
@@ -2166,7 +2166,7 @@
         <v>130</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2189,16 +2189,16 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2248,7 +2248,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>84</v>
@@ -2263,7 +2263,7 @@
         <v>76</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2360,13 +2360,13 @@
         <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>124</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -2405,7 +2405,7 @@
         <v>135</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2465,7 +2465,7 @@
         <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>82</v>
@@ -2479,7 +2479,7 @@
         <v>136</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2582,7 +2582,7 @@
         <v>137</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2611,7 +2611,7 @@
         <v>30</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2671,7 +2671,7 @@
         <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>82</v>
@@ -2685,7 +2685,7 @@
         <v>138</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2708,16 +2708,16 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2767,7 +2767,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>84</v>
@@ -2782,7 +2782,7 @@
         <v>76</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
@@ -2879,13 +2879,13 @@
         <v>84</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>124</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
@@ -3087,13 +3087,13 @@
         <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22">
@@ -3344,7 +3344,7 @@
         <v>165</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3404,7 +3404,7 @@
         <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>82</v>
@@ -3418,7 +3418,7 @@
         <v>166</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3521,7 +3521,7 @@
         <v>167</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3550,7 +3550,7 @@
         <v>30</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3610,7 +3610,7 @@
         <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>82</v>
@@ -3624,7 +3624,7 @@
         <v>168</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3647,16 +3647,16 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3706,7 +3706,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>84</v>
@@ -3721,7 +3721,7 @@
         <v>76</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -3818,13 +3818,13 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>124</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
@@ -3863,7 +3863,7 @@
         <v>30</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3923,7 +3923,7 @@
         <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>82</v>
@@ -3937,7 +3937,7 @@
         <v>172</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4040,7 +4040,7 @@
         <v>173</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4131,13 +4131,13 @@
         <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
@@ -4145,7 +4145,7 @@
         <v>174</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4168,16 +4168,16 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4227,7 +4227,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>84</v>
@@ -4242,7 +4242,7 @@
         <v>76</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
@@ -4339,21 +4339,21 @@
         <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>124</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4376,16 +4376,16 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -4435,7 +4435,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>84</v>
@@ -4450,7 +4450,7 @@
         <v>76</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35">
@@ -4547,13 +4547,13 @@
         <v>84</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>124</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-smartcard.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-smartcard.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T08:22:21+00:00</t>
+    <t>2024-07-02T09:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-smartcard.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-smartcard.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T09:45:37+00:00</t>
+    <t>2024-07-02T11:34:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-smartcard.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-smartcard.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:34:04+00:00</t>
+    <t>2024-07-02T11:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-smartcard.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-smartcard.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:51:09+00:00</t>
+    <t>2024-07-02T12:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-smartcard.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-smartcard.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:01:26+00:00</t>
+    <t>2024-07-02T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-smartcard.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-smartcard.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:28:16+00:00</t>
+    <t>2024-07-02T14:06:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-smartcard.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-smartcard.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T14:06:23+00:00</t>
+    <t>2024-07-09T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-smartcard.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-smartcard.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T09:28:43+00:00</t>
+    <t>2024-07-09T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
